--- a/artfynd/A 7039-2023 artfynd.xlsx
+++ b/artfynd/A 7039-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 7039-2023 artfynd.xlsx
+++ b/artfynd/A 7039-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105036372</v>
+        <v>105036392</v>
       </c>
       <c r="B2" t="n">
-        <v>77998</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1026</v>
+        <v>737</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Mörk kraterlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Gyalecta truncigena</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
+          <t>(Ach.) Hepp</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>700941.3248559423</v>
+        <v>700980</v>
       </c>
       <c r="R2" t="n">
-        <v>6363487.66518874</v>
+        <v>6363405</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2022-06-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105036436</v>
+        <v>105036365</v>
       </c>
       <c r="B3" t="n">
-        <v>42760</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79837</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101242</v>
+        <v>1026</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>700950.6489427376</v>
+        <v>700895</v>
       </c>
       <c r="R3" t="n">
-        <v>6363441.130760946</v>
+        <v>6363370</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +844,9 @@
           <t>2022-06-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,19 +877,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105036371</v>
+        <v>105036370</v>
       </c>
       <c r="B4" t="n">
-        <v>77998</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79837</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>700960.9304313923</v>
+        <v>700978</v>
       </c>
       <c r="R4" t="n">
-        <v>6363408.14682225</v>
+        <v>6363417</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,19 +945,9 @@
           <t>2022-06-27</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105036380</v>
+        <v>105036371</v>
       </c>
       <c r="B5" t="n">
-        <v>93158</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79837</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2818</v>
+        <v>1026</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>700869.7691585735</v>
+        <v>700961</v>
       </c>
       <c r="R5" t="n">
-        <v>6363434.99352812</v>
+        <v>6363408</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,19 +1046,9 @@
           <t>2022-06-27</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,19 +1079,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105036365</v>
+        <v>105036372</v>
       </c>
       <c r="B6" t="n">
-        <v>77998</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79837</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1179,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>700895.6771368331</v>
+        <v>700941</v>
       </c>
       <c r="R6" t="n">
-        <v>6363370.368131814</v>
+        <v>6363488</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,19 +1147,9 @@
           <t>2022-06-27</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,37 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105036425</v>
+        <v>105036383</v>
       </c>
       <c r="B7" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>76183</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>230185</v>
+        <v>1802</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Stor blanklav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Eopyrenula septemseptata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Coppins</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>700945.6473695862</v>
+        <v>700939</v>
       </c>
       <c r="R7" t="n">
-        <v>6363432.782514245</v>
+        <v>6363491</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1328,19 +1248,9 @@
           <t>2022-06-27</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,37 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>105036431</v>
+        <v>105036411</v>
       </c>
       <c r="B8" t="n">
-        <v>77412</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229183</v>
+        <v>2606</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Frostig asplav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lecidella laureri</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hepp) Körb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1411,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>700890.7649292119</v>
+        <v>700967</v>
       </c>
       <c r="R8" t="n">
-        <v>6363371.206959335</v>
+        <v>6363409</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1444,19 +1349,9 @@
           <t>2022-06-27</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,37 +1382,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>105036383</v>
+        <v>105036380</v>
       </c>
       <c r="B9" t="n">
-        <v>74428</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1802</v>
+        <v>2818</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor blanklav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Eopyrenula septemseptata</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Coppins</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1527,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>700939.0062759554</v>
+        <v>700870</v>
       </c>
       <c r="R9" t="n">
-        <v>6363490.792045057</v>
+        <v>6363435</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1560,19 +1450,9 @@
           <t>2022-06-27</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,37 +1483,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>105036392</v>
+        <v>105036435</v>
       </c>
       <c r="B10" t="n">
-        <v>79135</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>737</v>
+        <v>101242</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kraterlav</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gyalecta truncigena</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Hepp</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1643,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700980.0127696862</v>
+        <v>701004</v>
       </c>
       <c r="R10" t="n">
-        <v>6363405.304219292</v>
+        <v>6363470</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1676,19 +1551,9 @@
           <t>2022-06-27</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,37 +1584,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>105036411</v>
+        <v>105036436</v>
       </c>
       <c r="B11" t="n">
-        <v>95198</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2606</v>
+        <v>101242</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1759,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>700967.3828398893</v>
+        <v>700951</v>
       </c>
       <c r="R11" t="n">
-        <v>6363409.004306932</v>
+        <v>6363441</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1792,19 +1652,9 @@
           <t>2022-06-27</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,15 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>105036435</v>
+        <v>105036376</v>
       </c>
       <c r="B12" t="n">
-        <v>42760</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1851,21 +1696,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>101242</v>
+        <v>220299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1875,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>701003.3141044799</v>
+        <v>701031</v>
       </c>
       <c r="R12" t="n">
-        <v>6363470.728554334</v>
+        <v>6363452</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1908,19 +1753,9 @@
           <t>2022-06-27</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1951,37 +1786,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>105036370</v>
+        <v>105036431</v>
       </c>
       <c r="B13" t="n">
-        <v>77998</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79238</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1026</v>
+        <v>229183</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Frostig asplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Lecidella laureri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
+          <t>(Hepp) Körb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1991,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>700977.8099850236</v>
+        <v>700890</v>
       </c>
       <c r="R13" t="n">
-        <v>6363417.079318359</v>
+        <v>6363371</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2024,19 +1854,9 @@
           <t>2022-06-27</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2060,6 +1880,208 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>105036424</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Gajstmyr, Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>700972</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6363389</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-06-27</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-10-14</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>105036425</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Gajstmyr, Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>700946</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6363433</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-06-27</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-10-14</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
         <is>
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>

--- a/artfynd/A 7039-2023 artfynd.xlsx
+++ b/artfynd/A 7039-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105036392</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105036365</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105036370</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105036371</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105036372</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105036383</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105036411</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105036380</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105036435</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105036436</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105036376</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105036431</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,6 +2050,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105036424</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2086,8 +2156,29 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105036425</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>